--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1272,10 +1272,10 @@
         <v>13</v>
       </c>
       <c r="N21" t="n">
-        <v>15403.521040462</v>
+        <v>15403.521104651</v>
       </c>
       <c r="O21" t="n">
-        <v>200245.773526006</v>
+        <v>200245.774360463</v>
       </c>
       <c r="P21" t="n">
         <v>33500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964602273</v>
+        <v>15711.964444444</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.115056825</v>
+        <v>392799.1111111</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.81333333</v>
+        <v>174389.835</v>
       </c>
       <c r="O29" t="n">
-        <v>1220728.69333331</v>
+        <v>348779.67</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
       </c>
       <c r="Q29" t="n">
-        <v>2577400</v>
+        <v>736400</v>
       </c>
     </row>
     <row r="30">
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17847826</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.07106384</v>
+        <v>2067595.07086956</v>
       </c>
       <c r="P31" t="n">
         <v>532900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="O24" t="n">
-        <v>89070.211111112</v>
+        <v>106884.253333332</v>
       </c>
       <c r="P24" t="n">
         <v>46300</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.538745761</v>
+        <v>7945568.53721848</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1583,10 +1583,10 @@
         <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O28" t="n">
-        <v>4401588.44773582</v>
+        <v>4443508.33771438</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.569475157</v>
+        <v>4201315.635252812</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>74676.628235294</v>
+        <v>74676.625625</v>
       </c>
       <c r="O4" t="n">
-        <v>74676.628235294</v>
+        <v>74676.625625</v>
       </c>
       <c r="P4" t="n">
         <v>144900</v>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964444444</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.1111111</v>
+        <v>392799.10863095</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>26721.063333333</v>
+        <v>22267.553333333</v>
       </c>
       <c r="O24" t="n">
-        <v>106884.253333332</v>
+        <v>89070.21333333199</v>
       </c>
       <c r="P24" t="n">
         <v>46300</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141885.15245033</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O27" t="n">
-        <v>7945568.53721848</v>
+        <v>7919345.539602561</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1583,10 +1583,10 @@
         <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>201977.65171429</v>
+        <v>200072.20240385</v>
       </c>
       <c r="O28" t="n">
-        <v>4443508.33771438</v>
+        <v>4401588.4528847</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
@@ -1625,10 +1625,10 @@
         <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.835</v>
+        <v>174389.85125</v>
       </c>
       <c r="O29" t="n">
-        <v>348779.67</v>
+        <v>348779.7025</v>
       </c>
       <c r="P29" t="n">
         <v>368200</v>
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>62706.203511236</v>
+        <v>61666.874241573</v>
       </c>
       <c r="O35" t="n">
-        <v>4201315.635252812</v>
+        <v>4131680.574185391</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964345238</v>
+        <v>15711.964411765</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.10863095</v>
+        <v>392799.110294125</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1669,19 +1669,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>251809.29259259</v>
+        <v>251809.29230769</v>
       </c>
       <c r="O30" t="n">
-        <v>1259046.46296295</v>
+        <v>1007237.16923076</v>
       </c>
       <c r="P30" t="n">
         <v>584000</v>
       </c>
       <c r="Q30" t="n">
-        <v>2920000</v>
+        <v>2336000</v>
       </c>
     </row>
     <row r="31">
@@ -2235,10 +2235,10 @@
         <v>264</v>
       </c>
       <c r="N44" t="n">
-        <v>3340.6800838574</v>
+        <v>3340.6800840336</v>
       </c>
       <c r="O44" t="n">
-        <v>881939.5421383536</v>
+        <v>881939.5421848705</v>
       </c>
       <c r="P44" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964411765</v>
+        <v>15899.011607143</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.110294125</v>
+        <v>397475.290178575</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.17847826</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.07086956</v>
+        <v>2067595.07066664</v>
       </c>
       <c r="P31" t="n">
         <v>532900</v>
@@ -2682,10 +2682,10 @@
         <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>60174</v>
+        <v>61248.535714286</v>
       </c>
       <c r="O54" t="n">
-        <v>361044</v>
+        <v>367491.214285716</v>
       </c>
       <c r="P54" t="n">
         <v>96900</v>
@@ -2861,10 +2861,10 @@
         <v>144</v>
       </c>
       <c r="N58" t="n">
-        <v>25534</v>
+        <v>25576.890257559</v>
       </c>
       <c r="O58" t="n">
-        <v>3676896</v>
+        <v>3683072.197088496</v>
       </c>
       <c r="P58" t="n">
         <v>40900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O22" t="n">
-        <v>397475.290178575</v>
+        <v>392799.10863095</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -2682,10 +2682,10 @@
         <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>61248.535714286</v>
+        <v>60174</v>
       </c>
       <c r="O54" t="n">
-        <v>367491.214285716</v>
+        <v>361044</v>
       </c>
       <c r="P54" t="n">
         <v>96900</v>
@@ -2861,10 +2861,10 @@
         <v>144</v>
       </c>
       <c r="N58" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O58" t="n">
-        <v>3683072.197088496</v>
+        <v>3676896</v>
       </c>
       <c r="P58" t="n">
         <v>40900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964345238</v>
+        <v>15711.964135802</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.10863095</v>
+        <v>392799.10339505</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1669,19 +1669,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
         <v>251809.29230769</v>
       </c>
       <c r="O30" t="n">
-        <v>1007237.16923076</v>
+        <v>755427.8769230699</v>
       </c>
       <c r="P30" t="n">
         <v>584000</v>
       </c>
       <c r="Q30" t="n">
-        <v>2336000</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="31">
@@ -1875,10 +1875,10 @@
         <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.874241573</v>
+        <v>61666.874364162</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.574185391</v>
+        <v>4131680.582398854</v>
       </c>
       <c r="P35" t="n">
         <v>98900</v>
@@ -1999,10 +1999,10 @@
         <v>24</v>
       </c>
       <c r="N38" t="n">
-        <v>4878.2859393939</v>
+        <v>4878.2859756098</v>
       </c>
       <c r="O38" t="n">
-        <v>117078.8625454536</v>
+        <v>117078.8634146352</v>
       </c>
       <c r="P38" t="n">
         <v>13500</v>
@@ -2815,10 +2815,10 @@
         <v>300</v>
       </c>
       <c r="N57" t="n">
-        <v>18016</v>
+        <v>18023.2064</v>
       </c>
       <c r="O57" t="n">
-        <v>5404800</v>
+        <v>5406961.92</v>
       </c>
       <c r="P57" t="n">
         <v>29900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2815,10 +2815,10 @@
         <v>300</v>
       </c>
       <c r="N57" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O57" t="n">
-        <v>5406961.92</v>
+        <v>5404800</v>
       </c>
       <c r="P57" t="n">
         <v>29900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370787689</v>
+        <v>3926.8370772443</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.213521124</v>
+        <v>1272295.213027153</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -2235,10 +2235,10 @@
         <v>264</v>
       </c>
       <c r="N44" t="n">
-        <v>3340.6800840336</v>
+        <v>3340.6800842105</v>
       </c>
       <c r="O44" t="n">
-        <v>881939.5421848705</v>
+        <v>881939.542231572</v>
       </c>
       <c r="P44" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2410,10 +2410,10 @@
         <v>180</v>
       </c>
       <c r="N48" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O48" t="n">
-        <v>836748.0000000001</v>
+        <v>836894.361378348</v>
       </c>
       <c r="P48" t="n">
         <v>8900</v>
@@ -2549,10 +2549,10 @@
         <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O51" t="n">
-        <v>588912.48</v>
+        <v>610623.539170512</v>
       </c>
       <c r="P51" t="n">
         <v>52900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1580,31 +1580,28 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N28" t="n">
-        <v>200072.20240385</v>
+        <v>200072.2037234</v>
       </c>
       <c r="O28" t="n">
-        <v>4401588.4528847</v>
+        <v>2801010.8521276</v>
       </c>
       <c r="P28" t="n">
         <v>312000</v>
       </c>
       <c r="Q28" t="n">
-        <v>6864000</v>
+        <v>4368000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56404</v>
-      </c>
-      <c r="B29" t="n">
-        <v>6941607327999</v>
+        <v>62068</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>56404 PISCINA ESTRUCTURAL RECTANGULAR BESTWAY</t>
+          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1613,7 +1610,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1622,45 +1619,37 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>174389.85125</v>
+        <v>1977.88</v>
       </c>
       <c r="O29" t="n">
-        <v>348779.7025</v>
+        <v>11867.28</v>
       </c>
       <c r="P29" t="n">
-        <v>368200</v>
+        <v>2900</v>
       </c>
       <c r="Q29" t="n">
-        <v>736400</v>
+        <v>17400</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>56405</v>
-      </c>
-      <c r="B30" t="n">
-        <v>6941607328002</v>
+        <v>62091</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL RECTAGULAR BESTWAY 4.00mX2.11mX81cm</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1669,45 +1658,37 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="N30" t="n">
-        <v>251809.29230769</v>
+        <v>1141.57</v>
       </c>
       <c r="O30" t="n">
-        <v>755427.8769230699</v>
+        <v>247720.69</v>
       </c>
       <c r="P30" t="n">
-        <v>584000</v>
+        <v>3900</v>
       </c>
       <c r="Q30" t="n">
-        <v>1752000</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56417</v>
-      </c>
-      <c r="B31" t="n">
-        <v>6942138981902</v>
+        <v>67001</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piscina Estructural Redonda 366 x 76 cm Bomba/Filtro 56417</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1716,28 +1697,28 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>344599.17844444</v>
+        <v>26280.41</v>
       </c>
       <c r="O31" t="n">
-        <v>2067595.07066664</v>
+        <v>78841.23</v>
       </c>
       <c r="P31" t="n">
-        <v>532900</v>
+        <v>46500</v>
       </c>
       <c r="Q31" t="n">
-        <v>3197400</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>62068</v>
+        <v>67374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA EXTERIOR BESTWAY</t>
+          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1746,7 +1727,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1755,28 +1736,28 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="N32" t="n">
-        <v>1977.88</v>
+        <v>61666.874364162</v>
       </c>
       <c r="O32" t="n">
-        <v>11867.28</v>
+        <v>4131680.582398854</v>
       </c>
       <c r="P32" t="n">
-        <v>2900</v>
+        <v>98900</v>
       </c>
       <c r="Q32" t="n">
-        <v>17400</v>
+        <v>6626300</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62091</v>
+        <v>91004</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PARCHE PISCINA A PRUEBA DE AGUA BESTWAY</t>
+          <t>FLOTADOR DISNEY 56CM 24PCS</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1785,7 +1766,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1794,28 +1775,28 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="N33" t="n">
-        <v>1141.57</v>
+        <v>3865.67</v>
       </c>
       <c r="O33" t="n">
-        <v>247720.69</v>
+        <v>1314327.8</v>
       </c>
       <c r="P33" t="n">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="Q33" t="n">
-        <v>846300</v>
+        <v>1870000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67001</v>
+        <v>91007</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE SENCILLO BESTWAY 1.88 X 99 CM</t>
+          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1824,7 +1805,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1833,28 +1814,35 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>26280.41</v>
+        <v>16010.3</v>
       </c>
       <c r="O34" t="n">
-        <v>78841.23</v>
+        <v>384247.2</v>
       </c>
       <c r="P34" t="n">
-        <v>46500</v>
+        <v>30500</v>
       </c>
       <c r="Q34" t="n">
-        <v>139500</v>
+        <v>732000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>67374</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9103C</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>COLCHON INFLABLE DOBLE+ALMOHADAS BESTWAY 2.03mx1.52mx22cm</t>
+          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1863,7 +1851,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1872,28 +1860,30 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="N35" t="n">
-        <v>61666.874364162</v>
+        <v>4878.2859756098</v>
       </c>
       <c r="O35" t="n">
-        <v>4131680.582398854</v>
+        <v>117078.8634146352</v>
       </c>
       <c r="P35" t="n">
-        <v>98900</v>
+        <v>13500</v>
       </c>
       <c r="Q35" t="n">
-        <v>6626300</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>91004</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9103D</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FLOTADOR DISNEY 56CM 24PCS</t>
+          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1902,7 +1892,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>340</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1911,28 +1901,28 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>340</v>
+        <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>3865.67</v>
+        <v>7394.9355681818</v>
       </c>
       <c r="O36" t="n">
-        <v>1314327.8</v>
+        <v>88739.2268181816</v>
       </c>
       <c r="P36" t="n">
-        <v>5500</v>
+        <v>17900</v>
       </c>
       <c r="Q36" t="n">
-        <v>1870000</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91007</v>
+        <v>91040</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PISCINA DISNEY 122X25CM 12 PCS</t>
+          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1941,7 +1931,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1950,35 +1940,28 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="N37" t="n">
-        <v>16010.3</v>
+        <v>3114.49</v>
       </c>
       <c r="O37" t="n">
-        <v>384247.2</v>
+        <v>1252024.98</v>
       </c>
       <c r="P37" t="n">
-        <v>30500</v>
+        <v>5500</v>
       </c>
       <c r="Q37" t="n">
-        <v>732000</v>
+        <v>2211000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>9103C</t>
-        </is>
+      <c r="A38" t="n">
+        <v>91042</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9103C GAFA ACUATICA SIRENITA BESTWAY</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1987,7 +1970,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1996,30 +1979,28 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="N38" t="n">
-        <v>4878.2859756098</v>
+        <v>2791.02</v>
       </c>
       <c r="O38" t="n">
-        <v>117078.8634146352</v>
+        <v>334922.4</v>
       </c>
       <c r="P38" t="n">
-        <v>13500</v>
+        <v>3900</v>
       </c>
       <c r="Q38" t="n">
-        <v>324000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>9103D</t>
-        </is>
+      <c r="A39" t="n">
+        <v>91043</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9103D CARETA ACUATICA SIRENITA BESTWAY</t>
+          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2028,7 +2009,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2037,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="N39" t="n">
-        <v>7394.9355681818</v>
+        <v>3564.14</v>
       </c>
       <c r="O39" t="n">
-        <v>88739.2268181816</v>
+        <v>206720.12</v>
       </c>
       <c r="P39" t="n">
-        <v>17900</v>
+        <v>5500</v>
       </c>
       <c r="Q39" t="n">
-        <v>214800</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>91040</v>
+        <v>91098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FLOTADOR MINNIE 56CM 24 PCS</t>
+          <t>BALON INFLABLE MICKEY 51CM</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2067,7 +2048,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>402</v>
+        <v>183</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2076,28 +2057,28 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>402</v>
+        <v>183</v>
       </c>
       <c r="N40" t="n">
-        <v>3114.49</v>
+        <v>4378</v>
       </c>
       <c r="O40" t="n">
-        <v>1252024.98</v>
+        <v>801174</v>
       </c>
       <c r="P40" t="n">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="Q40" t="n">
-        <v>2211000</v>
+        <v>713700</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91042</v>
+        <v>98002</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA PRINCESAS 24 PCS</t>
+          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2106,7 +2087,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2115,28 +2096,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="N41" t="n">
-        <v>2791.02</v>
+        <v>3340.6800842105</v>
       </c>
       <c r="O41" t="n">
-        <v>334922.4</v>
+        <v>881939.542231572</v>
       </c>
       <c r="P41" t="n">
-        <v>3900</v>
+        <v>7100</v>
       </c>
       <c r="Q41" t="n">
-        <v>468000</v>
+        <v>1874400</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>91043</v>
+        <v>98003</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FLOTADOR PRINCESAS 56CM 24PCS</t>
+          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2145,7 +2126,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2154,28 +2135,35 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N42" t="n">
-        <v>3564.14</v>
+        <v>2903.52</v>
       </c>
       <c r="O42" t="n">
-        <v>206720.12</v>
+        <v>194535.84</v>
       </c>
       <c r="P42" t="n">
-        <v>5500</v>
+        <v>7100</v>
       </c>
       <c r="Q42" t="n">
-        <v>319000</v>
+        <v>475700</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>91098</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BALON INFLABLE MICKEY 51CM</t>
+          <t>SCOOTER COLORES</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2184,7 +2172,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2193,28 +2181,30 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="N43" t="n">
-        <v>4378</v>
+        <v>39171.85</v>
       </c>
       <c r="O43" t="n">
-        <v>801174</v>
+        <v>705093.2999999999</v>
       </c>
       <c r="P43" t="n">
-        <v>3900</v>
+        <v>68900</v>
       </c>
       <c r="Q43" t="n">
-        <v>713700</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>98002</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C1717</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA SIPDERMAN  51CM</t>
+          <t>ESPADA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2223,7 +2213,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>264</v>
+        <v>432</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2232,28 +2222,38 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>264</v>
+        <v>432</v>
       </c>
       <c r="N44" t="n">
-        <v>3340.6800842105</v>
+        <v>4443</v>
       </c>
       <c r="O44" t="n">
-        <v>881939.542231572</v>
+        <v>1919376</v>
       </c>
       <c r="P44" t="n">
-        <v>7100</v>
+        <v>6300</v>
       </c>
       <c r="Q44" t="n">
-        <v>1874400</v>
+        <v>2721600</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>98003</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C1758</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6914919067549</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FLOTADOR SPIDER MAN 56CM 24 PCS</t>
+          <t>MULA BLISTER SURTIDA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2271,30 +2271,33 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="N45" t="n">
-        <v>2903.52</v>
+        <v>4648.6</v>
       </c>
       <c r="O45" t="n">
-        <v>194535.84</v>
+        <v>836748.0000000001</v>
       </c>
       <c r="P45" t="n">
-        <v>7100</v>
+        <v>8900</v>
       </c>
       <c r="Q45" t="n">
-        <v>475700</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C105</t>
-        </is>
+          <t>C1897</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>6914919086373</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SCOOTER COLORES</t>
+          <t>MULA DIDACTICA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2308,7 +2311,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2317,30 +2320,30 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="N46" t="n">
-        <v>39171.85</v>
+        <v>16897</v>
       </c>
       <c r="O46" t="n">
-        <v>705093.2999999999</v>
+        <v>2433168</v>
       </c>
       <c r="P46" t="n">
-        <v>68900</v>
+        <v>27900</v>
       </c>
       <c r="Q46" t="n">
-        <v>1240200</v>
+        <v>4017600</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C1717</t>
+          <t>C2117</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ESPADA CON LUZ Y SONIDO</t>
+          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2349,7 +2352,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>432</v>
+        <v>1400</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2358,33 +2361,33 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>432</v>
+        <v>1400</v>
       </c>
       <c r="N47" t="n">
-        <v>4443</v>
+        <v>3751</v>
       </c>
       <c r="O47" t="n">
-        <v>1919376</v>
+        <v>5251400</v>
       </c>
       <c r="P47" t="n">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="Q47" t="n">
-        <v>2721600</v>
+        <v>8960000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C1758</t>
+          <t>C342</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6914919067549</v>
+        <v>6914919018374</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MULA BLISTER SURTIDA</t>
+          <t>COCINA CON VAPOR DE AGUA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2398,7 +2401,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2407,38 +2410,30 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="N48" t="n">
-        <v>4649.4131187686</v>
+        <v>24538.02</v>
       </c>
       <c r="O48" t="n">
-        <v>836894.361378348</v>
+        <v>588912.48</v>
       </c>
       <c r="P48" t="n">
-        <v>8900</v>
+        <v>52900</v>
       </c>
       <c r="Q48" t="n">
-        <v>1602000</v>
+        <v>1269600</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C1897</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>6914919086373</v>
+          <t>C3455</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MULA DIDACTICA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DINOSAURIO BOLSA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2447,7 +2442,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2456,30 +2451,35 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="N49" t="n">
-        <v>16897</v>
+        <v>5894.64</v>
       </c>
       <c r="O49" t="n">
-        <v>2433168</v>
+        <v>1697656.32</v>
       </c>
       <c r="P49" t="n">
-        <v>27900</v>
+        <v>11000</v>
       </c>
       <c r="Q49" t="n">
-        <v>4017600</v>
+        <v>3168000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C2117</t>
+          <t>C3638</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DISPLAY CARTÓN PEGAJOSOS X 20</t>
+          <t>INFLABLE DONA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2497,33 +2497,30 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1400</v>
+        <v>203</v>
       </c>
       <c r="N50" t="n">
-        <v>3751</v>
+        <v>3877.89</v>
       </c>
       <c r="O50" t="n">
-        <v>5251400</v>
+        <v>787211.6699999999</v>
       </c>
       <c r="P50" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="Q50" t="n">
-        <v>8960000</v>
+        <v>1319500</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C342</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>6914919018374</v>
+          <t>C3700</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COCINA CON VAPOR DE AGUA</t>
+          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2537,7 +2534,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2546,39 +2543,44 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>25442.647465438</v>
+        <v>60174</v>
       </c>
       <c r="O51" t="n">
-        <v>610623.539170512</v>
+        <v>361044</v>
       </c>
       <c r="P51" t="n">
-        <v>52900</v>
+        <v>96900</v>
       </c>
       <c r="Q51" t="n">
-        <v>1269600</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C3455</t>
+          <t>C3970</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DINOSAURIO BOLSA</t>
+          <t>GUITARRAS C3970</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2587,35 +2589,30 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="N52" t="n">
-        <v>5894.64</v>
+        <v>26854</v>
       </c>
       <c r="O52" t="n">
-        <v>1697656.32</v>
+        <v>1288992</v>
       </c>
       <c r="P52" t="n">
-        <v>11000</v>
+        <v>43900</v>
       </c>
       <c r="Q52" t="n">
-        <v>3168000</v>
+        <v>2107200</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C3638</t>
+          <t>C3988</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INFLABLE DONA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2624,7 +2621,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2633,30 +2630,30 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>3877.89</v>
+        <v>29700</v>
       </c>
       <c r="O53" t="n">
-        <v>787211.6699999999</v>
+        <v>356400</v>
       </c>
       <c r="P53" t="n">
-        <v>6500</v>
+        <v>50500</v>
       </c>
       <c r="Q53" t="n">
-        <v>1319500</v>
+        <v>606000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C3700</t>
+          <t>C4303</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MUNECA CON CARRO RECARGABLE DE CONTROL REMOTO</t>
+          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2666,11 +2663,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2679,30 +2676,30 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="N54" t="n">
-        <v>60174</v>
+        <v>18016</v>
       </c>
       <c r="O54" t="n">
-        <v>361044</v>
+        <v>5404800</v>
       </c>
       <c r="P54" t="n">
-        <v>96900</v>
+        <v>29900</v>
       </c>
       <c r="Q54" t="n">
-        <v>581400</v>
+        <v>8970000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C3970</t>
+          <t>C4305</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GUITARRAS C3970</t>
+          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2716,7 +2713,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2725,39 +2722,44 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="N55" t="n">
-        <v>26854</v>
+        <v>25534</v>
       </c>
       <c r="O55" t="n">
-        <v>1288992</v>
+        <v>3676896</v>
       </c>
       <c r="P55" t="n">
-        <v>43900</v>
+        <v>40900</v>
       </c>
       <c r="Q55" t="n">
-        <v>2107200</v>
+        <v>5889600</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C3988</t>
+          <t>C4310</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DRAGÓN CAMINA CON LUZ Y SONIDO</t>
+          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2766,30 +2768,30 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N56" t="n">
-        <v>29700</v>
+        <v>72889</v>
       </c>
       <c r="O56" t="n">
-        <v>356400</v>
+        <v>2332448</v>
       </c>
       <c r="P56" t="n">
-        <v>50500</v>
+        <v>117500</v>
       </c>
       <c r="Q56" t="n">
-        <v>606000</v>
+        <v>3760000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C4303</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BEBE CON PIJAMA MED BOLSA PVC C4303</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2803,7 +2805,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2812,30 +2814,30 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
-        <v>18016</v>
+        <v>27186</v>
       </c>
       <c r="O57" t="n">
-        <v>5404800</v>
+        <v>543720</v>
       </c>
       <c r="P57" t="n">
-        <v>29900</v>
+        <v>43900</v>
       </c>
       <c r="Q57" t="n">
-        <v>8970000</v>
+        <v>878000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C4305</t>
+          <t>C4728</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MUÑECA BEBE GRANDE CON PIJAMA EN BOLSA C4305</t>
+          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2849,7 +2851,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>144</v>
+        <v>1800</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2858,44 +2860,47 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>144</v>
+        <v>1800</v>
       </c>
       <c r="N58" t="n">
-        <v>25534</v>
+        <v>2454</v>
       </c>
       <c r="O58" t="n">
-        <v>3676896</v>
+        <v>4417200</v>
       </c>
       <c r="P58" t="n">
-        <v>40900</v>
+        <v>4200</v>
       </c>
       <c r="Q58" t="n">
-        <v>5889600</v>
+        <v>7560000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C4310</t>
-        </is>
+          <t>C488</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>6554632300006</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MUÑECA CON CARRO HUMO RECARGABLE C4310</t>
+          <t>MALETA JUGUETES</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2904,35 +2909,38 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="N59" t="n">
-        <v>72889</v>
+        <v>18491</v>
       </c>
       <c r="O59" t="n">
-        <v>2332448</v>
+        <v>221892</v>
       </c>
       <c r="P59" t="n">
-        <v>117500</v>
+        <v>13500</v>
       </c>
       <c r="Q59" t="n">
-        <v>3760000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C4545</t>
-        </is>
+          <t>C5032</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>6999899236154</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2941,7 +2949,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>20</v>
+        <v>937</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2950,30 +2958,30 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>20</v>
+        <v>937</v>
       </c>
       <c r="N60" t="n">
-        <v>27186</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>543720</v>
+        <v>8381821.06</v>
       </c>
       <c r="P60" t="n">
-        <v>43900</v>
+        <v>14900</v>
       </c>
       <c r="Q60" t="n">
-        <v>878000</v>
+        <v>13961300</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C4728</t>
+          <t>C698</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FLIOTADOR DONA DINOSAURIO #60 C4728</t>
+          <t>HELICE 9 LUCES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2983,11 +2991,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2996,33 +3004,30 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="N61" t="n">
-        <v>2454</v>
+        <v>1567.02</v>
       </c>
       <c r="O61" t="n">
-        <v>4417200</v>
+        <v>376084.8</v>
       </c>
       <c r="P61" t="n">
-        <v>4200</v>
+        <v>2900</v>
       </c>
       <c r="Q61" t="n">
-        <v>7560000</v>
+        <v>696000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C488</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>6554632300006</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MALETA JUGUETES</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3032,11 +3037,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3045,33 +3050,33 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N62" t="n">
-        <v>18491</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>221892</v>
+        <v>7963.099999999999</v>
       </c>
       <c r="P62" t="n">
-        <v>13500</v>
+        <v>2500</v>
       </c>
       <c r="Q62" t="n">
-        <v>162000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C5032</t>
+          <t>C7610</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6999899236154</v>
+        <v>6999899236093</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>INFLABLE TECHITO PIECITOS  FIGURAS STD C5032</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3085,7 +3090,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>937</v>
+        <v>360</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3094,159 +3099,18 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>937</v>
+        <v>360</v>
       </c>
       <c r="N63" t="n">
-        <v>8945.379999999999</v>
+        <v>7811.9</v>
       </c>
       <c r="O63" t="n">
-        <v>8381821.06</v>
+        <v>2812284</v>
       </c>
       <c r="P63" t="n">
-        <v>14900</v>
+        <v>13900</v>
       </c>
       <c r="Q63" t="n">
-        <v>13961300</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>C698</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>HELICE 9 LUCES</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>240</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>240</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1567.02</v>
-      </c>
-      <c r="O64" t="n">
-        <v>376084.8</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2900</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>696000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>C7560</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>10</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>10</v>
-      </c>
-      <c r="N65" t="n">
-        <v>796.3099999999999</v>
-      </c>
-      <c r="O65" t="n">
-        <v>7963.099999999999</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>C7610</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>6999899236093</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>360</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>360</v>
-      </c>
-      <c r="N66" t="n">
-        <v>7811.9</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2812284</v>
-      </c>
-      <c r="P66" t="n">
-        <v>13900</v>
-      </c>
-      <c r="Q66" t="n">
         <v>5004000</v>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.964135802</v>
+        <v>15711.963910256</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.10339505</v>
+        <v>392799.0977564</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1739,10 +1739,10 @@
         <v>67</v>
       </c>
       <c r="N32" t="n">
-        <v>61666.874364162</v>
+        <v>61666.874376812</v>
       </c>
       <c r="O32" t="n">
-        <v>4131680.582398854</v>
+        <v>4131680.583246404</v>
       </c>
       <c r="P32" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.963910256</v>
+        <v>15711.963831169</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.0977564</v>
+        <v>392799.095779225</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -2099,10 +2099,10 @@
         <v>264</v>
       </c>
       <c r="N41" t="n">
-        <v>3340.6800842105</v>
+        <v>3340.6800849257</v>
       </c>
       <c r="O41" t="n">
-        <v>881939.542231572</v>
+        <v>881939.5424203848</v>
       </c>
       <c r="P41" t="n">
         <v>7100</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370772443</v>
+        <v>3926.8370726607</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.213027153</v>
+        <v>1272295.211542067</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1233,10 +1233,10 @@
         <v>792</v>
       </c>
       <c r="N20" t="n">
-        <v>2681</v>
+        <v>2785.6243902439</v>
       </c>
       <c r="O20" t="n">
-        <v>2123352</v>
+        <v>2206214.517073169</v>
       </c>
       <c r="P20" t="n">
         <v>3500</v>
@@ -2912,10 +2912,10 @@
         <v>12</v>
       </c>
       <c r="N59" t="n">
-        <v>18491</v>
+        <v>19051.333333333</v>
       </c>
       <c r="O59" t="n">
-        <v>221892</v>
+        <v>228615.999999996</v>
       </c>
       <c r="P59" t="n">
         <v>13500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1233,10 +1233,10 @@
         <v>792</v>
       </c>
       <c r="N20" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O20" t="n">
-        <v>2206214.517073169</v>
+        <v>2123352</v>
       </c>
       <c r="P20" t="n">
         <v>3500</v>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.963831169</v>
+        <v>15711.96379085</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.095779225</v>
+        <v>392799.09477125</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -2912,10 +2912,10 @@
         <v>12</v>
       </c>
       <c r="N59" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O59" t="n">
-        <v>228615.999999996</v>
+        <v>221892</v>
       </c>
       <c r="P59" t="n">
         <v>13500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370726607</v>
+        <v>3926.8370711297</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.211542067</v>
+        <v>1272295.211046023</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.96379085</v>
+        <v>15711.96375</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.09477125</v>
+        <v>392799.09375</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-26</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -760,19 +760,19 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
         <v>13386</v>
       </c>
       <c r="O9" t="n">
-        <v>321264</v>
+        <v>160632</v>
       </c>
       <c r="P9" t="n">
         <v>23900</v>
       </c>
       <c r="Q9" t="n">
-        <v>573600</v>
+        <v>286800</v>
       </c>
     </row>
     <row r="10">
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.96375</v>
+        <v>15711.963708609</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.09375</v>
+        <v>392799.092715225</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88463576</v>
+        <v>141416.88465116</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.539602561</v>
+        <v>7919345.540464961</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1739,10 +1739,10 @@
         <v>67</v>
       </c>
       <c r="N32" t="n">
-        <v>61666.874376812</v>
+        <v>61666.874389535</v>
       </c>
       <c r="O32" t="n">
-        <v>4131680.583246404</v>
+        <v>4131680.584098845</v>
       </c>
       <c r="P32" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.211046023</v>
+        <v>1272295.209554748</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -2592,10 +2592,10 @@
         <v>48</v>
       </c>
       <c r="N52" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O52" t="n">
-        <v>1288992</v>
+        <v>1299884.890140864</v>
       </c>
       <c r="P52" t="n">
         <v>43900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1108,10 +1108,10 @@
         <v>324</v>
       </c>
       <c r="N17" t="n">
-        <v>3926.837066527</v>
+        <v>3926.837057278</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.209554748</v>
+        <v>1272295.206558072</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88465116</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.540464961</v>
+        <v>7919345.539602561</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -1739,10 +1739,10 @@
         <v>67</v>
       </c>
       <c r="N32" t="n">
-        <v>61666.874389535</v>
+        <v>61666.874467456</v>
       </c>
       <c r="O32" t="n">
-        <v>4131680.584098845</v>
+        <v>4131680.589319552</v>
       </c>
       <c r="P32" t="n">
         <v>98900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2592,10 +2592,10 @@
         <v>48</v>
       </c>
       <c r="N52" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O52" t="n">
-        <v>1299884.890140864</v>
+        <v>1288992</v>
       </c>
       <c r="P52" t="n">
         <v>43900</v>
@@ -2961,10 +2961,10 @@
         <v>937</v>
       </c>
       <c r="N60" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O60" t="n">
-        <v>8381821.06</v>
+        <v>8385599.491732519</v>
       </c>
       <c r="P60" t="n">
         <v>14900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>74676.625625</v>
+        <v>74676.599</v>
       </c>
       <c r="O4" t="n">
-        <v>74676.625625</v>
+        <v>74676.599</v>
       </c>
       <c r="P4" t="n">
         <v>144900</v>
@@ -635,10 +635,10 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>5758.9597772829</v>
+        <v>5758.9597767857</v>
       </c>
       <c r="O6" t="n">
-        <v>69107.5173273948</v>
+        <v>69107.5173214284</v>
       </c>
       <c r="P6" t="n">
         <v>16900</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1105,19 +1105,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>324</v>
+        <v>252</v>
       </c>
       <c r="N17" t="n">
         <v>3926.837057278</v>
       </c>
       <c r="O17" t="n">
-        <v>1272295.206558072</v>
+        <v>989562.938434056</v>
       </c>
       <c r="P17" t="n">
         <v>4800</v>
       </c>
       <c r="Q17" t="n">
-        <v>1555200</v>
+        <v>1209600</v>
       </c>
     </row>
     <row r="18">
@@ -1155,10 +1155,10 @@
         <v>12</v>
       </c>
       <c r="N18" t="n">
-        <v>22510.483207547</v>
+        <v>22510.483076923</v>
       </c>
       <c r="O18" t="n">
-        <v>270125.798490564</v>
+        <v>270125.796923076</v>
       </c>
       <c r="P18" t="n">
         <v>44900</v>
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="N27" t="n">
-        <v>141416.88463576</v>
+        <v>141416.88465116</v>
       </c>
       <c r="O27" t="n">
-        <v>7919345.539602561</v>
+        <v>7919345.540464961</v>
       </c>
       <c r="P27" t="n">
         <v>251900</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2057,19 +2057,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="N40" t="n">
         <v>4378</v>
       </c>
       <c r="O40" t="n">
-        <v>801174</v>
+        <v>591030</v>
       </c>
       <c r="P40" t="n">
         <v>3900</v>
       </c>
       <c r="Q40" t="n">
-        <v>713700</v>
+        <v>526500</v>
       </c>
     </row>
     <row r="41">
@@ -2961,10 +2961,10 @@
         <v>937</v>
       </c>
       <c r="N60" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>8385599.491732519</v>
+        <v>8381821.06</v>
       </c>
       <c r="P60" t="n">
         <v>14900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -2725,10 +2725,10 @@
         <v>144</v>
       </c>
       <c r="N55" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O55" t="n">
-        <v>3676896</v>
+        <v>3683188.463205888</v>
       </c>
       <c r="P55" t="n">
         <v>40900</v>

--- a/bodegas/CM-106.xlsx
+++ b/bodegas/CM-106.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1272,10 +1272,10 @@
         <v>13</v>
       </c>
       <c r="N21" t="n">
-        <v>15403.521104651</v>
+        <v>15403.521169591</v>
       </c>
       <c r="O21" t="n">
-        <v>200245.774360463</v>
+        <v>200245.775204683</v>
       </c>
       <c r="P21" t="n">
         <v>33500</v>
@@ -1314,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>15711.963708609</v>
+        <v>15711.963537415</v>
       </c>
       <c r="O22" t="n">
-        <v>392799.092715225</v>
+        <v>392799.088435375</v>
       </c>
       <c r="P22" t="n">
         <v>28500</v>
@@ -2725,10 +2725,10 @@
         <v>144</v>
       </c>
       <c r="N55" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O55" t="n">
-        <v>3683188.463205888</v>
+        <v>3676896</v>
       </c>
       <c r="P55" t="n">
         <v>40900</v>
